--- a/review-results/复盘信息抓取-20260822.xlsx
+++ b/review-results/复盘信息抓取-20260822.xlsx
@@ -1043,20 +1043,20 @@
   <dimension ref="A1:T97"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="7" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
     <col width="15" customWidth="1" min="16" max="16"/>
     <col width="17" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
@@ -5049,17 +5049,15 @@
   <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="2"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="7"/>
-    <col width="22" customWidth="1" min="8" max="9"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="8" max="9"/>
+    <col width="4" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6184,33 +6182,31 @@
   <dimension ref="A1:AB97"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="9" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="16"/>
-    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="26" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="8" customWidth="1" min="21" max="21"/>
-    <col width="8" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="24"/>
-    <col width="8" customWidth="1" min="24" max="24"/>
-    <col width="8" customWidth="1" min="25" max="26"/>
-    <col width="8" customWidth="1" min="26" max="26"/>
-    <col width="8" customWidth="1" min="27" max="27"/>
-    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="7" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="7" customWidth="1" min="23" max="24"/>
+    <col width="5" customWidth="1" min="25" max="26"/>
+    <col width="6" customWidth="1" min="27" max="27"/>
+    <col width="7" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15576,12 +15572,11 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="31" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="6"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="29" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18224,12 +18219,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
